--- a/business_surveys/034_investment_transition_survey--business_surveys.xlsx
+++ b/business_surveys/034_investment_transition_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -718,7 +718,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>hh:mm a</t>
+          <t>hh -mm a</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Follow Up Contact Other</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -928,7 +928,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Investment Type Other</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -951,7 +951,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Current Investment Advisor Other</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -974,7 +974,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Transition Date Other</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1001,12 +1001,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Transition Time Other</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>hh:mm a</t>
+          <t>hh -mm a</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Transition Duration Other</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>follow_up_contact_other</t>
+          <t>follow_up_contact_other_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Follow Up Contact Other 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Comments Other</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Additional Comments Other</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
